--- a/documentation/Construccion y Evolucion/1. Solicitudes de cambio/CR 3.xlsx
+++ b/documentation/Construccion y Evolucion/1. Solicitudes de cambio/CR 3.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Proyectos\TraductorBraille\documentation\Construccion y Evolucion\1. Solicitudes de cambio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\EPN\SEXTO SEMESTRE\Construccion y evolucion software\traductor_braile_español\TraductorBrailleEspanol\documentation\Construccion y Evolucion\1. Solicitudes de cambio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{655D4CCB-7891-4FB4-81FD-3CE47EFCD331}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" xr2:uid="{AAACD53E-982C-4521-B07F-7DC6290E23F5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040"/>
   </bookViews>
   <sheets>
     <sheet name="CR Formato" sheetId="1" r:id="rId1"/>
     <sheet name="Documento de Análisis" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -26,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="53">
   <si>
     <t>CHANGE REQUEST</t>
   </si>
@@ -152,13 +151,46 @@
   </si>
   <si>
     <t>Max Carrión</t>
+  </si>
+  <si>
+    <t>Generar un unico ejecutable del producto para su fácil instalación y posterior uso.</t>
+  </si>
+  <si>
+    <t>Codigo-Dependencias</t>
+  </si>
+  <si>
+    <t>Asegurarse de tener las librerias necesarias para el correcto funcionamiento de todas las funciones que ofrece el programa.</t>
+  </si>
+  <si>
+    <t>Clase ExportService</t>
+  </si>
+  <si>
+    <t>Clase VoiceService</t>
+  </si>
+  <si>
+    <t>Implementar la lógica necesaria para gestionar errores relacionados con dependencias y posibles conflictos durante la instalación.</t>
+  </si>
+  <si>
+    <t>Incorporar la lógica adecuada para manejar errores asociados con dependencias y conflictos en el proceso de instalación.</t>
+  </si>
+  <si>
+    <t>2 semanas</t>
+  </si>
+  <si>
+    <t>Alto</t>
+  </si>
+  <si>
+    <t>SoftTech</t>
+  </si>
+  <si>
+    <t>A</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -442,7 +474,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -482,6 +514,21 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -497,21 +544,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -532,6 +564,46 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -866,19 +938,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67F84A08-0160-4953-9528-DB07A5F993CD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:H33"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.375" defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="5.5703125" customWidth="1"/>
-    <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.5703125" customWidth="1"/>
-    <col min="5" max="7" width="20.140625" customWidth="1"/>
-    <col min="8" max="8" width="5.5703125" customWidth="1"/>
+    <col min="2" max="2" width="5.625" customWidth="1"/>
+    <col min="3" max="3" width="36.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.625" customWidth="1"/>
+    <col min="5" max="7" width="20.125" customWidth="1"/>
+    <col min="8" max="8" width="5.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:8" ht="15" thickBot="1"/>
+    <row r="2" spans="2:8">
       <c r="B2" s="1"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -887,7 +959,7 @@
       <c r="G2" s="2"/>
       <c r="H2" s="3"/>
     </row>
-    <row r="3" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:8" ht="18">
       <c r="B3" s="4"/>
       <c r="C3" s="5" t="s">
         <v>0</v>
@@ -899,22 +971,22 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:8">
       <c r="B4" s="4"/>
       <c r="F4" t="s">
         <v>2</v>
       </c>
       <c r="H4" s="6"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:8">
       <c r="B5" s="4"/>
       <c r="H5" s="7"/>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:8">
       <c r="B6" s="4"/>
       <c r="H6" s="7"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:8">
       <c r="B7" s="4"/>
       <c r="C7" t="s">
         <v>3</v>
@@ -927,15 +999,15 @@
       <c r="G7" s="25"/>
       <c r="H7" s="7"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:8">
       <c r="B8" s="4"/>
       <c r="H8" s="7"/>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8">
       <c r="B9" s="4"/>
       <c r="H9" s="7"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:8">
       <c r="B10" s="4"/>
       <c r="C10" t="s">
         <v>4</v>
@@ -948,11 +1020,11 @@
       <c r="G10" s="25"/>
       <c r="H10" s="7"/>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:8">
       <c r="B11" s="4"/>
       <c r="H11" s="7"/>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:8">
       <c r="B12" s="4"/>
       <c r="C12" t="s">
         <v>5</v>
@@ -965,47 +1037,47 @@
       <c r="G12" s="25"/>
       <c r="H12" s="7"/>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:8">
       <c r="B13" s="4"/>
       <c r="H13" s="7"/>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:8">
       <c r="B14" s="4"/>
       <c r="C14" t="s">
         <v>6</v>
       </c>
       <c r="H14" s="7"/>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:8">
       <c r="B15" s="4"/>
       <c r="C15" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="32"/>
-      <c r="E15" s="32"/>
-      <c r="F15" s="32"/>
-      <c r="G15" s="33"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="28"/>
       <c r="H15" s="7"/>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:8">
       <c r="B16" s="4"/>
-      <c r="C16" s="34"/>
-      <c r="D16" s="35"/>
-      <c r="E16" s="35"/>
-      <c r="F16" s="35"/>
-      <c r="G16" s="36"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="30"/>
+      <c r="E16" s="30"/>
+      <c r="F16" s="30"/>
+      <c r="G16" s="31"/>
       <c r="H16" s="7"/>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:8">
       <c r="B17" s="4"/>
       <c r="H17" s="7"/>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:8">
       <c r="B18" s="4"/>
-      <c r="C18" s="27" t="s">
+      <c r="C18" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="D18" s="28"/>
+      <c r="D18" s="33"/>
       <c r="E18" s="8" t="s">
         <v>8</v>
       </c>
@@ -1017,7 +1089,7 @@
       </c>
       <c r="H18" s="7"/>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:8">
       <c r="B19" s="4"/>
       <c r="C19" s="8" t="s">
         <v>11</v>
@@ -1034,40 +1106,58 @@
       <c r="G19" s="8"/>
       <c r="H19" s="7"/>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:8">
       <c r="B20" s="4"/>
       <c r="C20" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D20" s="9"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="8"/>
+      <c r="D20" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" s="10">
+        <v>45512</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>51</v>
+      </c>
       <c r="G20" s="8"/>
       <c r="H20" s="7"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:8">
       <c r="B21" s="4"/>
       <c r="C21" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D21" s="9"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="8"/>
+      <c r="D21" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E21" s="10">
+        <v>45516</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>51</v>
+      </c>
       <c r="G21" s="8"/>
       <c r="H21" s="7"/>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:8">
       <c r="B22" s="4"/>
       <c r="C22" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="9"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
+      <c r="D22" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="E22" s="10">
+        <v>45516</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>51</v>
+      </c>
       <c r="G22" s="8"/>
       <c r="H22" s="7"/>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:8">
       <c r="B23" s="4"/>
       <c r="C23" s="8" t="s">
         <v>16</v>
@@ -1078,7 +1168,7 @@
       <c r="G23" s="12"/>
       <c r="H23" s="7"/>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:8">
       <c r="B24" s="4"/>
       <c r="C24" s="8" t="s">
         <v>17</v>
@@ -1089,7 +1179,7 @@
       <c r="G24" s="12"/>
       <c r="H24" s="7"/>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:8">
       <c r="B25" s="4"/>
       <c r="C25" s="8" t="s">
         <v>18</v>
@@ -1100,7 +1190,7 @@
       <c r="G25" s="12"/>
       <c r="H25" s="7"/>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:8">
       <c r="B26" s="4"/>
       <c r="C26" s="8" t="s">
         <v>19</v>
@@ -1111,7 +1201,7 @@
       <c r="G26" s="12"/>
       <c r="H26" s="7"/>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:8">
       <c r="B27" s="4"/>
       <c r="C27" s="8" t="s">
         <v>20</v>
@@ -1122,7 +1212,7 @@
       <c r="G27" s="12"/>
       <c r="H27" s="7"/>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:8">
       <c r="B28" s="4"/>
       <c r="C28" s="8" t="s">
         <v>21</v>
@@ -1133,18 +1223,18 @@
       <c r="G28" s="12"/>
       <c r="H28" s="7"/>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:8">
       <c r="B29" s="4"/>
       <c r="H29" s="7"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:8">
       <c r="B30" s="4"/>
       <c r="C30" t="s">
         <v>22</v>
       </c>
       <c r="H30" s="7"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:8">
       <c r="B31" s="4"/>
       <c r="C31" s="13" t="s">
         <v>23</v>
@@ -1155,16 +1245,16 @@
       <c r="G31" s="13"/>
       <c r="H31" s="7"/>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:8">
       <c r="B32" s="4"/>
-      <c r="C32" s="29"/>
-      <c r="D32" s="30"/>
-      <c r="E32" s="30"/>
-      <c r="F32" s="30"/>
-      <c r="G32" s="31"/>
+      <c r="C32" s="34"/>
+      <c r="D32" s="35"/>
+      <c r="E32" s="35"/>
+      <c r="F32" s="35"/>
+      <c r="G32" s="36"/>
       <c r="H32" s="7"/>
     </row>
-    <row r="33" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:8" ht="15" thickBot="1">
       <c r="B33" s="14"/>
       <c r="C33" s="15"/>
       <c r="D33" s="15"/>
@@ -1175,31 +1265,31 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="C32:G32"/>
     <mergeCell ref="D7:G7"/>
     <mergeCell ref="D10:G10"/>
     <mergeCell ref="D12:G12"/>
     <mergeCell ref="C15:G16"/>
     <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C32:G32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33198599-D7F8-440A-9813-85D60D291D95}">
-  <dimension ref="B1:H34"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B1:H33"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.375" defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="3.5703125" customWidth="1"/>
+    <col min="2" max="2" width="3.625" customWidth="1"/>
     <col min="3" max="3" width="39" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.85546875" customWidth="1"/>
-    <col min="6" max="6" width="22.140625" customWidth="1"/>
-    <col min="8" max="8" width="7.7109375" customWidth="1"/>
+    <col min="4" max="4" width="24.875" customWidth="1"/>
+    <col min="6" max="6" width="22.125" customWidth="1"/>
+    <col min="8" max="8" width="7.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:8" ht="15" thickBot="1"/>
+    <row r="2" spans="2:8">
       <c r="B2" s="1"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -1208,7 +1298,7 @@
       <c r="G2" s="2"/>
       <c r="H2" s="3"/>
     </row>
-    <row r="3" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:8" ht="18">
       <c r="B3" s="4"/>
       <c r="C3" s="5" t="s">
         <v>24</v>
@@ -1216,45 +1306,53 @@
       <c r="F3" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="17"/>
+      <c r="G3" s="17">
+        <v>3</v>
+      </c>
       <c r="H3" s="7"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:8">
       <c r="B4" s="4"/>
       <c r="F4" t="s">
         <v>26</v>
       </c>
-      <c r="G4" s="18"/>
+      <c r="G4" s="18">
+        <v>3</v>
+      </c>
       <c r="H4" s="7"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:8">
       <c r="B5" s="4"/>
       <c r="F5" t="s">
         <v>27</v>
       </c>
-      <c r="G5" s="18"/>
+      <c r="G5" s="44">
+        <v>45516</v>
+      </c>
       <c r="H5" s="7"/>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:8">
       <c r="B6" s="4"/>
       <c r="H6" s="7"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:8">
       <c r="B7" s="4"/>
       <c r="C7" t="s">
         <v>3</v>
       </c>
-      <c r="D7" s="37"/>
+      <c r="D7" s="37" t="s">
+        <v>36</v>
+      </c>
       <c r="E7" s="37"/>
       <c r="F7" s="37"/>
       <c r="G7" s="37"/>
       <c r="H7" s="7"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:8">
       <c r="B8" s="4"/>
       <c r="H8" s="7"/>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8">
       <c r="B9" s="4"/>
       <c r="C9" s="19" t="s">
         <v>28</v>
@@ -1265,160 +1363,178 @@
       <c r="G9" s="21"/>
       <c r="H9" s="7"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:8">
       <c r="B10" s="4"/>
-      <c r="C10" s="38"/>
-      <c r="D10" s="39"/>
-      <c r="E10" s="39"/>
-      <c r="F10" s="39"/>
-      <c r="G10" s="40"/>
+      <c r="C10" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" s="46"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="46"/>
+      <c r="G10" s="47"/>
       <c r="H10" s="7"/>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:8">
       <c r="B11" s="4"/>
-      <c r="C11" s="38"/>
-      <c r="D11" s="39"/>
-      <c r="E11" s="39"/>
-      <c r="F11" s="39"/>
-      <c r="G11" s="40"/>
+      <c r="C11" s="45"/>
+      <c r="D11" s="46"/>
+      <c r="E11" s="46"/>
+      <c r="F11" s="46"/>
+      <c r="G11" s="47"/>
       <c r="H11" s="7"/>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:8">
       <c r="B12" s="4"/>
-      <c r="C12" s="38"/>
-      <c r="D12" s="39"/>
-      <c r="E12" s="39"/>
-      <c r="F12" s="39"/>
-      <c r="G12" s="40"/>
+      <c r="C12" s="45"/>
+      <c r="D12" s="46"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="46"/>
+      <c r="G12" s="47"/>
       <c r="H12" s="7"/>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:8">
       <c r="B13" s="4"/>
-      <c r="C13" s="38"/>
-      <c r="D13" s="39"/>
-      <c r="E13" s="39"/>
-      <c r="F13" s="39"/>
-      <c r="G13" s="40"/>
+      <c r="C13" s="45"/>
+      <c r="D13" s="46"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="46"/>
+      <c r="G13" s="47"/>
       <c r="H13" s="7"/>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:8">
       <c r="B14" s="4"/>
-      <c r="C14" s="41"/>
-      <c r="D14" s="42"/>
-      <c r="E14" s="42"/>
-      <c r="F14" s="42"/>
-      <c r="G14" s="43"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="49"/>
+      <c r="E14" s="49"/>
+      <c r="F14" s="49"/>
+      <c r="G14" s="50"/>
       <c r="H14" s="7"/>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:8">
       <c r="B15" s="4"/>
       <c r="H15" s="7"/>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:8">
       <c r="B16" s="4"/>
       <c r="C16" t="s">
         <v>29</v>
       </c>
       <c r="H16" s="7"/>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:8">
       <c r="B17" s="4"/>
       <c r="C17" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="D17" s="29" t="s">
+      <c r="D17" s="34" t="s">
         <v>31</v>
       </c>
-      <c r="E17" s="30"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="31"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="35"/>
+      <c r="G17" s="36"/>
       <c r="H17" s="7"/>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:8" ht="31.5" customHeight="1">
       <c r="B18" s="4"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="29"/>
-      <c r="E18" s="30"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="31"/>
+      <c r="C18" s="57" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" s="51" t="s">
+        <v>44</v>
+      </c>
+      <c r="E18" s="52"/>
+      <c r="F18" s="52"/>
+      <c r="G18" s="53"/>
       <c r="H18" s="7"/>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:8" ht="28.5" customHeight="1">
       <c r="B19" s="4"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="29"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="31"/>
+      <c r="C19" s="57" t="s">
+        <v>45</v>
+      </c>
+      <c r="D19" s="54" t="s">
+        <v>47</v>
+      </c>
+      <c r="E19" s="55"/>
+      <c r="F19" s="55"/>
+      <c r="G19" s="56"/>
       <c r="H19" s="7"/>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:8" ht="27.75" customHeight="1">
       <c r="B20" s="4"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="29"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="31"/>
+      <c r="C20" s="57" t="s">
+        <v>46</v>
+      </c>
+      <c r="D20" s="54" t="s">
+        <v>48</v>
+      </c>
+      <c r="E20" s="55"/>
+      <c r="F20" s="55"/>
+      <c r="G20" s="56"/>
       <c r="H20" s="7"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:8">
       <c r="B21" s="4"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="29"/>
-      <c r="E21" s="30"/>
-      <c r="F21" s="30"/>
-      <c r="G21" s="31"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="39"/>
       <c r="H21" s="7"/>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:8">
       <c r="B22" s="4"/>
-      <c r="F22" s="39"/>
-      <c r="G22" s="39"/>
+      <c r="C22" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>49</v>
+      </c>
       <c r="H22" s="7"/>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:8">
       <c r="B23" s="4"/>
-      <c r="C23" t="s">
-        <v>32</v>
-      </c>
-      <c r="D23" s="17"/>
       <c r="H23" s="7"/>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:8">
       <c r="B24" s="4"/>
+      <c r="C24" t="s">
+        <v>33</v>
+      </c>
       <c r="H24" s="7"/>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:8">
       <c r="B25" s="4"/>
       <c r="C25" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="D25" s="17" t="s">
+        <v>50</v>
       </c>
       <c r="H25" s="7"/>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:8">
       <c r="B26" s="4"/>
-      <c r="C26" t="s">
-        <v>34</v>
-      </c>
-      <c r="D26" s="17"/>
       <c r="H26" s="7"/>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:8">
       <c r="B27" s="4"/>
+      <c r="C27" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="D27" s="20"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="21"/>
       <c r="H27" s="7"/>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:8">
       <c r="B28" s="4"/>
-      <c r="C28" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="21"/>
+      <c r="C28" s="38"/>
+      <c r="D28" s="39"/>
+      <c r="E28" s="39"/>
+      <c r="F28" s="39"/>
+      <c r="G28" s="40"/>
       <c r="H28" s="7"/>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:8">
       <c r="B29" s="4"/>
       <c r="C29" s="38"/>
       <c r="D29" s="39"/>
@@ -1427,7 +1543,7 @@
       <c r="G29" s="40"/>
       <c r="H29" s="7"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:8">
       <c r="B30" s="4"/>
       <c r="C30" s="38"/>
       <c r="D30" s="39"/>
@@ -1436,7 +1552,7 @@
       <c r="G30" s="40"/>
       <c r="H30" s="7"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:8">
       <c r="B31" s="4"/>
       <c r="C31" s="38"/>
       <c r="D31" s="39"/>
@@ -1445,67 +1561,40 @@
       <c r="G31" s="40"/>
       <c r="H31" s="7"/>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:8">
       <c r="B32" s="4"/>
-      <c r="C32" s="38"/>
-      <c r="D32" s="39"/>
-      <c r="E32" s="39"/>
-      <c r="F32" s="39"/>
-      <c r="G32" s="40"/>
+      <c r="C32" s="41"/>
+      <c r="D32" s="42"/>
+      <c r="E32" s="42"/>
+      <c r="F32" s="42"/>
+      <c r="G32" s="43"/>
       <c r="H32" s="7"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33" s="4"/>
-      <c r="C33" s="41"/>
-      <c r="D33" s="42"/>
-      <c r="E33" s="42"/>
-      <c r="F33" s="42"/>
-      <c r="G33" s="43"/>
-      <c r="H33" s="7"/>
-    </row>
-    <row r="34" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="14"/>
-      <c r="C34" s="15"/>
-      <c r="D34" s="15"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="15"/>
-      <c r="G34" s="15"/>
-      <c r="H34" s="16"/>
+    <row r="33" spans="2:8" ht="15" thickBot="1">
+      <c r="B33" s="14"/>
+      <c r="C33" s="15"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="15"/>
+      <c r="H33" s="16"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="D7:G7"/>
     <mergeCell ref="C10:G14"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="C29:G33"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C28:G32"/>
     <mergeCell ref="D17:G17"/>
     <mergeCell ref="D18:G18"/>
     <mergeCell ref="D19:G19"/>
     <mergeCell ref="D20:G20"/>
-    <mergeCell ref="D21:G21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="f7b1a7ea-1dd0-43bd-8f52-dd9459d0ec96" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B08EDF72D49EA44AB90F024D99D2B5E3" ma:contentTypeVersion="17" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="d6207507167e209dbfd27b884ee120ca">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="f7b1a7ea-1dd0-43bd-8f52-dd9459d0ec96" xmlns:ns4="56eae398-d265-4f71-b30c-62c529056c9f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7ebf290c66ec3e245dfaec660d84bc70" ns3:_="" ns4:_="">
     <xsd:import namespace="f7b1a7ea-1dd0-43bd-8f52-dd9459d0ec96"/>
@@ -1752,32 +1841,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{96BACB75-2D9E-4BF9-B15E-EA86EAB29BB3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="f7b1a7ea-1dd0-43bd-8f52-dd9459d0ec96"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="56eae398-d265-4f71-b30c-62c529056c9f"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3BE880B-0D64-411C-BD75-74863A321A9B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="f7b1a7ea-1dd0-43bd-8f52-dd9459d0ec96" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A299727D-0257-4624-9B82-EEF7D307A1F7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1794,4 +1875,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3BE880B-0D64-411C-BD75-74863A321A9B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{96BACB75-2D9E-4BF9-B15E-EA86EAB29BB3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="f7b1a7ea-1dd0-43bd-8f52-dd9459d0ec96"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="56eae398-d265-4f71-b30c-62c529056c9f"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>